--- a/noted.xlsx
+++ b/noted.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thainamthip2-my.sharepoint.com/personal/sutripat_ng_thainamthip_co_th/Documents/1. Work/008. Procurement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_F25DC773A252ABDACC10485A31DD4BD65ADE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49BEB64A-90DA-4CB0-AEBF-4764C7AB5BD7}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="11_F25DC773A252ABDACC10485A31DD4BD65ADE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDE2B7A9-3512-43AB-8A66-6E9AEBBC7E90}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Link for MSForm" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="44">
   <si>
     <r>
       <t xml:space="preserve">ปัจจุบัน Vendor Evaluation มีทั้งหมด   </t>
@@ -101,6 +102,84 @@
   </si>
   <si>
     <t>แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ (Outsource Other&amp;Miscellanous)  – Fill out form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ปัจจุบัน Vendor Evaluation มีทั้งหมด </t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>WASTE</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>Logistic</t>
+  </si>
+  <si>
+    <t>Agile</t>
+  </si>
+  <si>
+    <t>Property</t>
+  </si>
+  <si>
+    <t>Energy&amp;Chemical</t>
+  </si>
+  <si>
+    <t>Outsource (Group2)</t>
+  </si>
+  <si>
+    <t>แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ Manufacturing_N</t>
+  </si>
+  <si>
+    <t>แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ IT</t>
+  </si>
+  <si>
+    <t>แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ (Outsource)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ (Outsource Other&amp;Miscellanous) </t>
+  </si>
+  <si>
+    <t>แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ (Agile)</t>
+  </si>
+  <si>
+    <t>RawMat &amp; PKG (QA)</t>
+  </si>
+  <si>
+    <t>RawMat &amp; PKG (Procurement)</t>
+  </si>
+  <si>
+    <t>RawMat &amp; PKG (Store)</t>
+  </si>
+  <si>
+    <t>RawMat &amp; PKG (Packaging)</t>
+  </si>
+  <si>
+    <t>แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ RM&amp;PKG (QA)</t>
+  </si>
+  <si>
+    <t>แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ RM&amp;PKG (PROCUREMENT)</t>
+  </si>
+  <si>
+    <t>แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ RM&amp;PKG (STORE)</t>
+  </si>
+  <si>
+    <t>แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ RM&amp;PKG (PACKAGING)</t>
+  </si>
+  <si>
+    <t>Topic</t>
   </si>
 </sst>
 </file>
@@ -662,4 +741,277 @@
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;9&amp;K000000 Classified - Internal Use</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8186BF0-D448-46BA-8642-69132F5481B2}">
+  <sheetPr>
+    <tabColor theme="1"/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.75" customWidth="1"/>
+    <col min="2" max="2" width="33.9140625" customWidth="1"/>
+    <col min="3" max="3" width="74.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.08203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C18" s="5"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C20" s="5"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" display="https://forms.office.com/Pages/DesignPageV2.aspx?subpage=design&amp;FormId=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BUOExPSEY4UFpBR0pQUlpWRkZGMExSQVc0WSQlQCN0PWcu&amp;Token=844849531256498b9082ed49fa34613f" xr:uid="{FED02D22-1E60-43AF-9E9A-967BA9085309}"/>
+    <hyperlink ref="C4" r:id="rId2" display="https://forms.office.com/pages/responsepage.aspx?id=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BUREVHUFgwUUtJV0NSOU42VlZMMjlFWEg0NSQlQCN0PWcu&amp;route=shorturl" xr:uid="{E24FAE71-06DD-4993-AAFE-705C89AB0216}"/>
+    <hyperlink ref="C5" r:id="rId3" display="https://forms.office.com/pages/responsepage.aspx?id=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BURFFRNTM3VUtVVlNEU09WUVQ5UjdER0hEQiQlQCN0PWcu&amp;route=shorturl" xr:uid="{77810DEA-591E-4D28-881F-F4BA42E434DE}"/>
+    <hyperlink ref="D5" r:id="rId4" display="https://forms.office.com/Pages/DesignPageV2.aspx?subpage=design&amp;FormId=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BURFFRNTM3VUtVVlNEU09WUVQ5UjdER0hEQiQlQCN0PWcu&amp;Token=3763d99764c84fd3ab48de4e8e85cb45" xr:uid="{BC031FC2-6C2F-4B8F-BEE4-A41485A03AD7}"/>
+    <hyperlink ref="C3" r:id="rId5" display="https://forms.office.com/pages/responsepage.aspx?id=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BUMUtDQUI5RUNaNko0MlFCNEdRQVVCSDdQMyQlQCN0PWcu&amp;route=shorturl" xr:uid="{014702D3-C1C2-4A4B-8705-3E6A4170ACE6}"/>
+    <hyperlink ref="D6" r:id="rId6" display="แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ (Outsource Other&amp;Miscellanous) " xr:uid="{E43B3C88-1907-485E-A675-272522B16509}"/>
+    <hyperlink ref="C6" r:id="rId7" display="https://forms.office.com/Pages/ResponsePage.aspx?id=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BURDIxRTcxU1JaTDBDNURVM1RFQTVVSk84QSQlQCN0PWcu" xr:uid="{B09A2F82-58E5-4712-B1DD-989BF912DB9C}"/>
+    <hyperlink ref="C7" r:id="rId8" display="https://forms.office.com/pages/responsepage.aspx?id=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BUNjk5V1RBQzVNM1BTNzRXSUtaUkRNM1BPOSQlQCN0PWcu&amp;route=shorturl" xr:uid="{7CD503E8-78E8-44AB-AAFF-FDA39BB4CAA3}"/>
+    <hyperlink ref="D7" r:id="rId9" display="https://forms.office.com/Pages/DesignPageV2.aspx?subpage=design&amp;FormId=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BUNjk5V1RBQzVNM1BTNzRXSUtaUkRNM1BPOSQlQCN0PWcu&amp;Token=dab2d9c0e40544ceaba42aa4c390551f" xr:uid="{DFC64FF7-553C-46A9-ABB5-7899507DC7BE}"/>
+    <hyperlink ref="C8" r:id="rId10" display="https://forms.office.com/pages/responsepage.aspx?id=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BUMzZGS0NaVjk1VlhZUERIOFE1QUFaOTQzUiQlQCN0PWcu&amp;route=shorturl" xr:uid="{6DE85B43-927A-43E9-A02D-1F936B43B5ED}"/>
+    <hyperlink ref="D8" r:id="rId11" display="https://forms.office.com/Pages/DesignPageV2.aspx?subpage=design&amp;FormId=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BUMzZGS0NaVjk1VlhZUERIOFE1QUFaOTQzUiQlQCN0PWcu&amp;Token=34d7d720f45044b8adc555cca2df4664" xr:uid="{4732F308-4770-42E4-91E5-30F49D9B94D5}"/>
+    <hyperlink ref="C9" r:id="rId12" display="https://forms.office.com/pages/responsepage.aspx?id=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BUOFRIVFBYS1dJSktSUzExNlJUVFBZMEZVMiQlQCN0PWcu&amp;route=shorturl" xr:uid="{C0D2B8C2-B536-463D-892A-349F049EC59C}"/>
+    <hyperlink ref="D9" r:id="rId13" display="https://forms.office.com/Pages/DesignPageV2.aspx?subpage=design&amp;FormId=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BUOFRIVFBYS1dJSktSUzExNlJUVFBZMEZVMiQlQCN0PWcu&amp;Token=3804f8edafd7429592c2292f954427e9" xr:uid="{98C3F504-37A2-4EF1-AAD8-B5893089BC10}"/>
+    <hyperlink ref="C10" r:id="rId14" xr:uid="{AD650708-2BFF-48B8-8FB8-38C33A835A74}"/>
+    <hyperlink ref="C11" r:id="rId15" display="https://forms.office.com/pages/responsepage.aspx?id=OTkkUKki40eRjoa3Rpl77BNLJ1z-El5MpvJuIrSsSqBUNFZYWjZEUE5QSktMTEkxS0szNEhDUlhOTC4u&amp;route=shorturl" xr:uid="{56587B18-F5C7-40E9-928F-C327A62F2D51}"/>
+    <hyperlink ref="D11" r:id="rId16" display="https://forms.office.com/Pages/DesignPageV2.aspx?subpage=design&amp;FormId=OTkkUKki40eRjoa3Rpl77BNLJ1z-El5MpvJuIrSsSqBUNFZYWjZEUE5QSktMTEkxS0szNEhDUlhOTC4u&amp;Token=ebdb13eef1ae40d394a5136af1403ef4" xr:uid="{B6DB4A68-235A-4AAF-8FBA-72F18F561B1D}"/>
+    <hyperlink ref="C12" r:id="rId17" display="https://forms.office.com/pages/responsepage.aspx?id=OTkkUKki40eRjoa3Rpl77BNLJ1z-El5MpvJuIrSsSqBUREEzUzgxUTdLVzExN0o5MkFDTTZKSlVOUy4u&amp;route=shorturl" xr:uid="{6F3A4040-1EB4-4410-9625-8942D6EBB550}"/>
+    <hyperlink ref="D12" r:id="rId18" display="https://forms.office.com/Pages/DesignPageV2.aspx?subpage=design&amp;FormId=OTkkUKki40eRjoa3Rpl77BNLJ1z-El5MpvJuIrSsSqBUREEzUzgxUTdLVzExN0o5MkFDTTZKSlVOUy4u&amp;Token=26a68b8d6f074a97b97921841722c3f8" xr:uid="{F71B7B1A-9DD2-413B-9449-3C5C0AA779F6}"/>
+    <hyperlink ref="D4" r:id="rId19" display="https://forms.office.com/Pages/DesignPageV2.aspx?subpage=design&amp;FormId=OTkkUKki40eRjoa3Rpl77JYAPzHU61xNhx1hgCp991BUREVHUFgwUUtJV0NSOU42VlZMMjlFWEg0NSQlQCN0PWcu&amp;Token=2b653d20a84e464faf95647b159cfc83" xr:uid="{BC6F18B8-876A-4843-BF7A-60C7975BEB6E}"/>
+    <hyperlink ref="D10" r:id="rId20" display="แบบประเมินคุณภาพการส่งมอบสินค้า/บริการ  (Agile)" xr:uid="{575CFB3A-48F9-48F2-8C5B-FA8F67A80CD2}"/>
+    <hyperlink ref="D13" r:id="rId21" xr:uid="{43752E67-F5C3-4B81-A155-A51979211691}"/>
+    <hyperlink ref="C13" r:id="rId22" xr:uid="{42088436-C204-4E38-A562-572242505CCA}"/>
+    <hyperlink ref="D14" r:id="rId23" xr:uid="{F7E6A438-32C8-4CF3-8D14-8454C9251FB5}"/>
+    <hyperlink ref="C14" r:id="rId24" xr:uid="{A68A1E16-3A7C-4300-A9EC-75C3E9C261F8}"/>
+    <hyperlink ref="D15" r:id="rId25" xr:uid="{4DE470CE-DC89-4D45-9C8E-38C40C7E3C81}"/>
+    <hyperlink ref="C15" r:id="rId26" xr:uid="{DBB729DB-E74B-4364-80E4-48846E6D93CA}"/>
+    <hyperlink ref="D16" r:id="rId27" xr:uid="{33F986E9-8D13-4DDD-9B46-BA3F782860A3}"/>
+    <hyperlink ref="C16" r:id="rId28" xr:uid="{F82165F2-7A82-4542-8492-D25AA7E24171}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;9&amp;K000000 Classified - Internal Use</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>